--- a/rkgroup_site/leads.xlsx
+++ b/rkgroup_site/leads.xlsx
@@ -49,8 +49,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -524,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -564,6 +567,82 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>Дата</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>прив</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>g@gmal.com</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>acjnwcdncnjsdcnsdjcnsdnjcsdvnsvjnxajsncajxnasjxjncjdacndjncdjcjvnscjdcjncscnvccnvjfvjnvnfnvsadcdscndsjcnsdcnd</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-03-31 16:45:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>hjhjhu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>gm@gm.gm</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>dkfjnqdk</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-04-01 09:21:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>efenwf</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>d@djdn.jfdj</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>ndjndjvdnv</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-04-01 09:22:11</t>
         </is>
       </c>
     </row>
